--- a/CSC-580-Advanced-Software-Engineering/Project Management Assignments/PM Assignment 2/user stories.xlsx
+++ b/CSC-580-Advanced-Software-Engineering/Project Management Assignments/PM Assignment 2/user stories.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZRD25\Documents\GitHub\ai-masters-workspace-1\CSC-580-Advanced-Software-Engineering\Project Management Assignments\PM Assignment 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://generalmotors-my.sharepoint.com/personal/yzrd25_nam_corp_gm_com/Documents/Desktop/ai-masters-workspace/CSC-580-Advanced-Software-Engineering/Project Management Assignments/PM Assignment 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{686C91D1-A742-4326-BEE0-09F5BC83DEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{686C91D1-A742-4326-BEE0-09F5BC83DEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AABBFE26-F5B3-4AED-A3B1-088FB83878D5}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{55A9A4B4-9092-4B3B-872D-476CAE86D8BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{55A9A4B4-9092-4B3B-872D-476CAE86D8BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Payment" sheetId="7" r:id="rId1"/>
@@ -33,8 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="42">
   <si>
     <t xml:space="preserve">Use Case Name: </t>
   </si>
@@ -165,13 +163,16 @@
   </si>
   <si>
     <t>6. The app updates when a new transaction is made (App)</t>
+  </si>
+  <si>
+    <t>Story Points:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,11 +333,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -346,49 +368,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -397,12 +403,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -738,153 +738,307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D121AEF6-4219-44CD-A5C0-648243AED36A}">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" customHeight="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+    </row>
+    <row r="6" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="4" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="12" t="s">
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M10" s="15"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="M10" s="5"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="1">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="33">
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:F1"/>
@@ -896,6 +1050,7 @@
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="D7:K7"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -904,152 +1059,152 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36E8E8A-17D2-42A9-AD29-3672A3B6A77E}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" customHeight="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+    </row>
+    <row r="6" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="4" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="12" t="s">
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M10" s="15"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="M10" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:F1"/>
@@ -1061,6 +1216,7 @@
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="D7:K7"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1069,152 +1225,152 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53B6771-691F-4FDF-9B27-33F25105E435}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" customHeight="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+    </row>
+    <row r="6" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="4" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="12" t="s">
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M10" s="15"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="M10" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="A3:C8"/>
     <mergeCell ref="A1:C1"/>
@@ -1226,6 +1382,7 @@
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="D7:K7"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1234,152 +1391,152 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB956C9-7EB1-44CA-8CF9-CCB5982A2899}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" customHeight="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:13" ht="35.25" customHeight="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+    </row>
+    <row r="6" spans="1:13" ht="47.25" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:13" ht="51" customHeight="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="37.5" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
       <c r="D8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="18"/>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M10" s="15"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="M10" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="A3:C8"/>
     <mergeCell ref="A1:C1"/>
@@ -1391,6 +1548,7 @@
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="D7:K7"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1399,154 +1557,154 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C609E763-134F-411B-B208-A3C24D8C964D}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" customHeight="1">
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="3" t="s">
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" spans="1:13" ht="31.5" customHeight="1">
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M10" s="15"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="M10" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="D9:K9"/>
     <mergeCell ref="A1:C1"/>
@@ -1559,6 +1717,7 @@
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="D7:K7"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1567,154 +1726,154 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2049E8-1F11-40DC-B9BC-D4B94C0AACFB}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" customHeight="1">
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="3" t="s">
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" spans="1:13" ht="31.5" customHeight="1">
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M10" s="15"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="M10" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="A3:C9"/>
     <mergeCell ref="D9:K9"/>
@@ -1727,6 +1886,7 @@
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="D7:K7"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1736,136 +1896,136 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63AF6AA9-C790-4DF3-93B4-EE2801A4EB93}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" spans="1:11" ht="42.75" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="A3:C8"/>
     <mergeCell ref="A1:C1"/>
@@ -1877,6 +2037,7 @@
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="D7:K7"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
